--- a/2018/Beirut1/Beirut1_members_final.xlsx
+++ b/2018/Beirut1/Beirut1_members_final.xlsx
@@ -472,7 +472,7 @@
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>مستقل</t>
         </is>
       </c>
     </row>
@@ -499,7 +499,7 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>مستقل</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>مستقل</t>
         </is>
       </c>
     </row>
@@ -553,7 +553,7 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>مستقل</t>
         </is>
       </c>
     </row>
@@ -715,7 +715,7 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>مستقل</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
       </c>
       <c r="E20" s="6" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>مستقل</t>
         </is>
       </c>
     </row>
@@ -1228,7 +1228,7 @@
       </c>
       <c r="E30" s="8" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>مستقل</t>
         </is>
       </c>
     </row>
@@ -1255,7 +1255,7 @@
       </c>
       <c r="E31" s="8" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>مستقل</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="E34" s="8" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>مستقل</t>
         </is>
       </c>
     </row>
